--- a/example/template.xlsx
+++ b/example/template.xlsx
@@ -410,13 +410,14 @@
       <c r="D7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="0"/>
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -477,7 +478,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B12:E18"/>
   </mergeCells>
   <hyperlinks>

--- a/example/template.xlsx
+++ b/example/template.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">{{range .items}}</t>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">{{ .quantity | format_number }}</t>
   </si>
   <si>
-    <t xml:space="preserve">{{ .price | multiply .quantity | format_number }}</t>
+    <t xml:space="preserve">{{ .date | format_date }}</t>
   </si>
   <si>
     <t xml:space="preserve">{{end}}</t>
@@ -410,7 +410,6 @@
       <c r="D7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
       <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
